--- a/Structure_Data/text.9.14/20260914_211/structure_factor_20260914_211.xlsx
+++ b/Structure_Data/text.9.14/20260914_211/structure_factor_20260914_211.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D373"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -248,6 +248,3939 @@
         <v>12.2541831101235</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度 beta / Constrictivity (x)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈半径 r_min (um)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔体半径 r_max (um)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度状态 / Constrictivity Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">侵入入口 / Intrusion Inlet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球心邻域 / Center Connectivity</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法版本 / Method</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edt_critical_radii_closed_dilation_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径采样 / Radius Sampling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All positive EDT values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius (um)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPSD (total volume fraction)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIP (total volume fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.394660949707031</v>
+      </c>
+      <c r="C30">
+        <v>0.393535614013672</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
+      <c r="B31">
+        <v>0.394660949707031</v>
+      </c>
+      <c r="C31">
+        <v>0.393535614013672</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B32">
+        <v>0.287841796875</v>
+      </c>
+      <c r="C32">
+        <v>0.236289978027344</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B33">
+        <v>0.13787841796875</v>
+      </c>
+      <c r="C33">
+        <v>0.0114631652832031</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>0.0916061401367188</v>
+      </c>
+      <c r="C34">
+        <v>0.00214385986328125</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B35">
+        <v>0.0646400451660156</v>
+      </c>
+      <c r="C35">
+        <v>0.00052642822265625</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B36">
+        <v>0.0136337280273438</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B37">
+        <v>0.00570297241210938</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>1.5</v>
+      </c>
+      <c r="B38">
+        <v>0.00191879272460938</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>2</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弦长分布 / Chord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_voxel_runs_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>33243</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>1.55608699575851</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>1.37040493290319</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window-spanning lines</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full pore line policy</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one_period_censored</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.05</v>
+      </c>
+      <c r="B55">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.1</v>
+      </c>
+      <c r="B56">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.15</v>
+      </c>
+      <c r="B57">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.2</v>
+      </c>
+      <c r="B58">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.25</v>
+      </c>
+      <c r="B59">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.3</v>
+      </c>
+      <c r="B60">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.35</v>
+      </c>
+      <c r="B61">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.4</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.45</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.5</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.55</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.6</v>
+      </c>
+      <c r="B66">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.7</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.75</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.8</v>
+      </c>
+      <c r="B70">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.85</v>
+      </c>
+      <c r="B71">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.9</v>
+      </c>
+      <c r="B72">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.95</v>
+      </c>
+      <c r="B73">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.5</v>
+      </c>
+      <c r="B75">
+        <v>11639</v>
+      </c>
+      <c r="C75">
+        <v>0.350118822007641</v>
+      </c>
+      <c r="D75">
+        <v>0.350118822007641</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>1</v>
+      </c>
+      <c r="B76">
+        <v>6973</v>
+      </c>
+      <c r="C76">
+        <v>0.209758445386999</v>
+      </c>
+      <c r="D76">
+        <v>0.559877267394639</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>1.5</v>
+      </c>
+      <c r="B77">
+        <v>4619</v>
+      </c>
+      <c r="C77">
+        <v>0.138946545137322</v>
+      </c>
+      <c r="D77">
+        <v>0.698823812531962</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>2</v>
+      </c>
+      <c r="B78">
+        <v>3004</v>
+      </c>
+      <c r="C78">
+        <v>0.0903648888487802</v>
+      </c>
+      <c r="D78">
+        <v>0.789188701380742</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>2.5</v>
+      </c>
+      <c r="B79">
+        <v>2080</v>
+      </c>
+      <c r="C79">
+        <v>0.0625695635171314</v>
+      </c>
+      <c r="D79">
+        <v>0.851758264897873</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>3</v>
+      </c>
+      <c r="B80">
+        <v>1419</v>
+      </c>
+      <c r="C80">
+        <v>0.0426856781878892</v>
+      </c>
+      <c r="D80">
+        <v>0.894443943085762</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>3.5</v>
+      </c>
+      <c r="B81">
+        <v>971</v>
+      </c>
+      <c r="C81">
+        <v>0.0292091568149686</v>
+      </c>
+      <c r="D81">
+        <v>0.923653099900731</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>4</v>
+      </c>
+      <c r="B82">
+        <v>736</v>
+      </c>
+      <c r="C82">
+        <v>0.0221399993983696</v>
+      </c>
+      <c r="D82">
+        <v>0.945793099299101</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>4.5</v>
+      </c>
+      <c r="B83">
+        <v>545</v>
+      </c>
+      <c r="C83">
+        <v>0.0163944289023253</v>
+      </c>
+      <c r="D83">
+        <v>0.962187528201426</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>5</v>
+      </c>
+      <c r="B84">
+        <v>362</v>
+      </c>
+      <c r="C84">
+        <v>0.0108895105736546</v>
+      </c>
+      <c r="D84">
+        <v>0.97307703877508</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>5.5</v>
+      </c>
+      <c r="B85">
+        <v>277</v>
+      </c>
+      <c r="C85">
+        <v>0.00833258129531029</v>
+      </c>
+      <c r="D85">
+        <v>0.981409620070391</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>6</v>
+      </c>
+      <c r="B86">
+        <v>192</v>
+      </c>
+      <c r="C86">
+        <v>0.00577565201696598</v>
+      </c>
+      <c r="D86">
+        <v>0.987185272087357</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>6.5</v>
+      </c>
+      <c r="B87">
+        <v>113</v>
+      </c>
+      <c r="C87">
+        <v>0.00339921186415185</v>
+      </c>
+      <c r="D87">
+        <v>0.990584483951509</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>7</v>
+      </c>
+      <c r="B88">
+        <v>106</v>
+      </c>
+      <c r="C88">
+        <v>0.00318864121769997</v>
+      </c>
+      <c r="D88">
+        <v>0.993773125169209</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>7.5</v>
+      </c>
+      <c r="B89">
+        <v>66</v>
+      </c>
+      <c r="C89">
+        <v>0.00198538038083205</v>
+      </c>
+      <c r="D89">
+        <v>0.995758505550041</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>8</v>
+      </c>
+      <c r="B90">
+        <v>39</v>
+      </c>
+      <c r="C90">
+        <v>0.00117317931594621</v>
+      </c>
+      <c r="D90">
+        <v>0.996931684865987</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>8.5</v>
+      </c>
+      <c r="B91">
+        <v>36</v>
+      </c>
+      <c r="C91">
+        <v>0.00108293475318112</v>
+      </c>
+      <c r="D91">
+        <v>0.998014619619168</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>9</v>
+      </c>
+      <c r="B92">
+        <v>27</v>
+      </c>
+      <c r="C92">
+        <v>0.000812201064885841</v>
+      </c>
+      <c r="D92">
+        <v>0.998826820684054</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>9.5</v>
+      </c>
+      <c r="B93">
+        <v>8</v>
+      </c>
+      <c r="C93">
+        <v>0.000240652167373582</v>
+      </c>
+      <c r="D93">
+        <v>0.999067472851427</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>10</v>
+      </c>
+      <c r="B94">
+        <v>9</v>
+      </c>
+      <c r="C94">
+        <v>0.00027073368829528</v>
+      </c>
+      <c r="D94">
+        <v>0.999338206539723</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>10.5</v>
+      </c>
+      <c r="B95">
+        <v>7</v>
+      </c>
+      <c r="C95">
+        <v>0.000210570646451885</v>
+      </c>
+      <c r="D95">
+        <v>0.999548777186175</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>11</v>
+      </c>
+      <c r="B96">
+        <v>2</v>
+      </c>
+      <c r="C96">
+        <v>6.01630418433956e-05</v>
+      </c>
+      <c r="D96">
+        <v>0.999608940228018</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>11.5</v>
+      </c>
+      <c r="B97">
+        <v>6</v>
+      </c>
+      <c r="C97">
+        <v>0.000180489125530187</v>
+      </c>
+      <c r="D97">
+        <v>0.999789429353548</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>13</v>
+      </c>
+      <c r="B98">
+        <v>2</v>
+      </c>
+      <c r="C98">
+        <v>6.01630418433956e-05</v>
+      </c>
+      <c r="D98">
+        <v>0.999849592395392</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>13.5</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99">
+        <v>3.00815209216978e-05</v>
+      </c>
+      <c r="D99">
+        <v>0.999879673916313</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>14.5</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100">
+        <v>3.00815209216978e-05</v>
+      </c>
+      <c r="D100">
+        <v>0.999909755437235</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>15</v>
+      </c>
+      <c r="B101">
+        <v>2</v>
+      </c>
+      <c r="C101">
+        <v>6.01630418433956e-05</v>
+      </c>
+      <c r="D101">
+        <v>0.999969918479078</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>15.5</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102">
+        <v>3.00815209216978e-05</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球接触分布 / Spherical Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_solid_to_pore_edt_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>158686</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>0.67278673277038</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>0.365591808838336</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance direction</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solid_to_pore</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance convention</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voxel_center_to_voxel_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>0.05</v>
+      </c>
+      <c r="B117">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>0.1</v>
+      </c>
+      <c r="B118">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>0.15</v>
+      </c>
+      <c r="B119">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>0.2</v>
+      </c>
+      <c r="B120">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>0.25</v>
+      </c>
+      <c r="B121">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>0.3</v>
+      </c>
+      <c r="B122">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>0.35</v>
+      </c>
+      <c r="B123">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>0.4</v>
+      </c>
+      <c r="B124">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>0.45</v>
+      </c>
+      <c r="B125">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>0.5</v>
+      </c>
+      <c r="B126">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>0.55</v>
+      </c>
+      <c r="B127">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>0.6</v>
+      </c>
+      <c r="B128">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>0.65</v>
+      </c>
+      <c r="B129">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>0.7</v>
+      </c>
+      <c r="B130">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>0.75</v>
+      </c>
+      <c r="B131">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>0.8</v>
+      </c>
+      <c r="B132">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>0.85</v>
+      </c>
+      <c r="B133">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>0.9</v>
+      </c>
+      <c r="B134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>0.95</v>
+      </c>
+      <c r="B135">
+        <v>1.22474487139159</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>0.5</v>
+      </c>
+      <c r="B137">
+        <v>97757</v>
+      </c>
+      <c r="C137">
+        <v>0.616040482462221</v>
+      </c>
+      <c r="D137">
+        <v>0.616040482462221</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B138">
+        <v>35516</v>
+      </c>
+      <c r="C138">
+        <v>0.223813064794626</v>
+      </c>
+      <c r="D138">
+        <v>0.839853547256847</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B139">
+        <v>8032</v>
+      </c>
+      <c r="C139">
+        <v>0.0506156812825328</v>
+      </c>
+      <c r="D139">
+        <v>0.89046922853938</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>1</v>
+      </c>
+      <c r="B140">
+        <v>4347</v>
+      </c>
+      <c r="C140">
+        <v>0.0273937209331636</v>
+      </c>
+      <c r="D140">
+        <v>0.917862949472543</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B141">
+        <v>4114</v>
+      </c>
+      <c r="C141">
+        <v>0.0259254124497435</v>
+      </c>
+      <c r="D141">
+        <v>0.943788361922287</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B142">
+        <v>1524</v>
+      </c>
+      <c r="C142">
+        <v>0.00960387179713396</v>
+      </c>
+      <c r="D142">
+        <v>0.953392233719421</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B143">
+        <v>600</v>
+      </c>
+      <c r="C143">
+        <v>0.00378105188863542</v>
+      </c>
+      <c r="D143">
+        <v>0.957173285608056</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>1.5</v>
+      </c>
+      <c r="B144">
+        <v>1222</v>
+      </c>
+      <c r="C144">
+        <v>0.0077007423465208</v>
+      </c>
+      <c r="D144">
+        <v>0.964874027954577</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B145">
+        <v>661</v>
+      </c>
+      <c r="C145">
+        <v>0.00416545883064669</v>
+      </c>
+      <c r="D145">
+        <v>0.969039486785224</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B146">
+        <v>489</v>
+      </c>
+      <c r="C146">
+        <v>0.00308155728923787</v>
+      </c>
+      <c r="D146">
+        <v>0.972121044074462</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B147">
+        <v>158</v>
+      </c>
+      <c r="C147">
+        <v>0.00099567699734066</v>
+      </c>
+      <c r="D147">
+        <v>0.973116721071802</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B148">
+        <v>413</v>
+      </c>
+      <c r="C148">
+        <v>0.00260262405001071</v>
+      </c>
+      <c r="D148">
+        <v>0.975719345121813</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B149">
+        <v>617</v>
+      </c>
+      <c r="C149">
+        <v>0.00388818169214676</v>
+      </c>
+      <c r="D149">
+        <v>0.97960752681396</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>2</v>
+      </c>
+      <c r="B150">
+        <v>137</v>
+      </c>
+      <c r="C150">
+        <v>0.000863340181238421</v>
+      </c>
+      <c r="D150">
+        <v>0.980470866995198</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B151">
+        <v>481</v>
+      </c>
+      <c r="C151">
+        <v>0.00303114326405606</v>
+      </c>
+      <c r="D151">
+        <v>0.983502010259254</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B152">
+        <v>271</v>
+      </c>
+      <c r="C152">
+        <v>0.00170777510303366</v>
+      </c>
+      <c r="D152">
+        <v>0.985209785362288</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B153">
+        <v>170</v>
+      </c>
+      <c r="C153">
+        <v>0.00107129803511337</v>
+      </c>
+      <c r="D153">
+        <v>0.986281083397401</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B154">
+        <v>151</v>
+      </c>
+      <c r="C154">
+        <v>0.00095156472530658</v>
+      </c>
+      <c r="D154">
+        <v>0.987232648122708</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B155">
+        <v>244</v>
+      </c>
+      <c r="C155">
+        <v>0.00153762776804507</v>
+      </c>
+      <c r="D155">
+        <v>0.988770275890753</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B156">
+        <v>119</v>
+      </c>
+      <c r="C156">
+        <v>0.000749908624579358</v>
+      </c>
+      <c r="D156">
+        <v>0.989520184515332</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B157">
+        <v>108</v>
+      </c>
+      <c r="C157">
+        <v>0.000680589339954375</v>
+      </c>
+      <c r="D157">
+        <v>0.990200773855286</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>2.5</v>
+      </c>
+      <c r="B158">
+        <v>165</v>
+      </c>
+      <c r="C158">
+        <v>0.00103978926937474</v>
+      </c>
+      <c r="D158">
+        <v>0.991240563124661</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B159">
+        <v>214</v>
+      </c>
+      <c r="C159">
+        <v>0.0013485751736133</v>
+      </c>
+      <c r="D159">
+        <v>0.992589138298275</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>2.59807621135332</v>
+      </c>
+      <c r="B160">
+        <v>82</v>
+      </c>
+      <c r="C160">
+        <v>0.000516743758113507</v>
+      </c>
+      <c r="D160">
+        <v>0.993105882056388</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>2.69258240356725</v>
+      </c>
+      <c r="B161">
+        <v>167</v>
+      </c>
+      <c r="C161">
+        <v>0.00105239277567019</v>
+      </c>
+      <c r="D161">
+        <v>0.994158274832058</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>2.73861278752583</v>
+      </c>
+      <c r="B162">
+        <v>84</v>
+      </c>
+      <c r="C162">
+        <v>0.000529347264408959</v>
+      </c>
+      <c r="D162">
+        <v>0.994687622096467</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>2.82842712474619</v>
+      </c>
+      <c r="B163">
+        <v>16</v>
+      </c>
+      <c r="C163">
+        <v>0.000100828050363611</v>
+      </c>
+      <c r="D163">
+        <v>0.994788450146831</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>2.87228132326901</v>
+      </c>
+      <c r="B164">
+        <v>65</v>
+      </c>
+      <c r="C164">
+        <v>0.00040961395460217</v>
+      </c>
+      <c r="D164">
+        <v>0.995198064101433</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>2.91547594742265</v>
+      </c>
+      <c r="B165">
+        <v>73</v>
+      </c>
+      <c r="C165">
+        <v>0.000460027979783976</v>
+      </c>
+      <c r="D165">
+        <v>0.995658092081217</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>2.95803989154981</v>
+      </c>
+      <c r="B166">
+        <v>43</v>
+      </c>
+      <c r="C166">
+        <v>0.000270975385352205</v>
+      </c>
+      <c r="D166">
+        <v>0.995929067466569</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>3</v>
+      </c>
+      <c r="B167">
+        <v>54</v>
+      </c>
+      <c r="C167">
+        <v>0.000340294669977188</v>
+      </c>
+      <c r="D167">
+        <v>0.996269362136546</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>3.04138126514911</v>
+      </c>
+      <c r="B168">
+        <v>31</v>
+      </c>
+      <c r="C168">
+        <v>0.000195354347579497</v>
+      </c>
+      <c r="D168">
+        <v>0.996464716484126</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>3.08220700148449</v>
+      </c>
+      <c r="B169">
+        <v>61</v>
+      </c>
+      <c r="C169">
+        <v>0.000384406942011268</v>
+      </c>
+      <c r="D169">
+        <v>0.996849123426137</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="B170">
+        <v>27</v>
+      </c>
+      <c r="C170">
+        <v>0.000170147334988594</v>
+      </c>
+      <c r="D170">
+        <v>0.997019270761126</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>3.20156211871642</v>
+      </c>
+      <c r="B171">
+        <v>83</v>
+      </c>
+      <c r="C171">
+        <v>0.000523045511261233</v>
+      </c>
+      <c r="D171">
+        <v>0.997542316272387</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>3.24037034920393</v>
+      </c>
+      <c r="B172">
+        <v>21</v>
+      </c>
+      <c r="C172">
+        <v>0.00013233681610224</v>
+      </c>
+      <c r="D172">
+        <v>0.997674653088489</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>3.278719262151</v>
+      </c>
+      <c r="B173">
+        <v>12</v>
+      </c>
+      <c r="C173">
+        <v>7.56210377727084e-05</v>
+      </c>
+      <c r="D173">
+        <v>0.997750274126262</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>3.3166247903554</v>
+      </c>
+      <c r="B174">
+        <v>17</v>
+      </c>
+      <c r="C174">
+        <v>0.000107129803511337</v>
+      </c>
+      <c r="D174">
+        <v>0.997857403929773</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>3.35410196624968</v>
+      </c>
+      <c r="B175">
+        <v>31</v>
+      </c>
+      <c r="C175">
+        <v>0.000195354347579497</v>
+      </c>
+      <c r="D175">
+        <v>0.998052758277353</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>3.39116499156263</v>
+      </c>
+      <c r="B176">
+        <v>23</v>
+      </c>
+      <c r="C176">
+        <v>0.000144940322397691</v>
+      </c>
+      <c r="D176">
+        <v>0.99819769859975</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>3.46410161513775</v>
+      </c>
+      <c r="B177">
+        <v>5</v>
+      </c>
+      <c r="C177">
+        <v>3.15087657386285e-05</v>
+      </c>
+      <c r="D177">
+        <v>0.998229207365489</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>3.5</v>
+      </c>
+      <c r="B178">
+        <v>38</v>
+      </c>
+      <c r="C178">
+        <v>0.000239466619613576</v>
+      </c>
+      <c r="D178">
+        <v>0.998468673985103</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>3.53553390593274</v>
+      </c>
+      <c r="B179">
+        <v>41</v>
+      </c>
+      <c r="C179">
+        <v>0.000258371879056754</v>
+      </c>
+      <c r="D179">
+        <v>0.998727045864159</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>3.57071421427143</v>
+      </c>
+      <c r="B180">
+        <v>17</v>
+      </c>
+      <c r="C180">
+        <v>0.000107129803511337</v>
+      </c>
+      <c r="D180">
+        <v>0.998834175667671</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>3.60555127546399</v>
+      </c>
+      <c r="B181">
+        <v>9</v>
+      </c>
+      <c r="C181">
+        <v>5.67157783295313e-05</v>
+      </c>
+      <c r="D181">
+        <v>0.998890891446</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>3.64005494464026</v>
+      </c>
+      <c r="B182">
+        <v>20</v>
+      </c>
+      <c r="C182">
+        <v>0.000126035062954514</v>
+      </c>
+      <c r="D182">
+        <v>0.999016926508955</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>3.67423461417477</v>
+      </c>
+      <c r="B183">
+        <v>23</v>
+      </c>
+      <c r="C183">
+        <v>0.000144940322397691</v>
+      </c>
+      <c r="D183">
+        <v>0.999161866831352</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>3.74165738677394</v>
+      </c>
+      <c r="B184">
+        <v>10</v>
+      </c>
+      <c r="C184">
+        <v>6.3017531477257e-05</v>
+      </c>
+      <c r="D184">
+        <v>0.99922488436283</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>3.77491721763537</v>
+      </c>
+      <c r="B185">
+        <v>15</v>
+      </c>
+      <c r="C185">
+        <v>9.45262972158855e-05</v>
+      </c>
+      <c r="D185">
+        <v>0.999319410660046</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>3.80788655293195</v>
+      </c>
+      <c r="B186">
+        <v>6</v>
+      </c>
+      <c r="C186">
+        <v>3.78105188863542e-05</v>
+      </c>
+      <c r="D186">
+        <v>0.999357221178932</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>3.8405728739343</v>
+      </c>
+      <c r="B187">
+        <v>14</v>
+      </c>
+      <c r="C187">
+        <v>8.82245440681598e-05</v>
+      </c>
+      <c r="D187">
+        <v>0.999445445723</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>3.90512483795333</v>
+      </c>
+      <c r="B188">
+        <v>13</v>
+      </c>
+      <c r="C188">
+        <v>8.19227909204341e-05</v>
+      </c>
+      <c r="D188">
+        <v>0.999527368513921</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>3.93700393700591</v>
+      </c>
+      <c r="B189">
+        <v>11</v>
+      </c>
+      <c r="C189">
+        <v>6.93192846249827e-05</v>
+      </c>
+      <c r="D189">
+        <v>0.999596687798546</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>4</v>
+      </c>
+      <c r="B190">
+        <v>4</v>
+      </c>
+      <c r="C190">
+        <v>2.52070125909028e-05</v>
+      </c>
+      <c r="D190">
+        <v>0.999621894811137</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>4.03112887414927</v>
+      </c>
+      <c r="B191">
+        <v>13</v>
+      </c>
+      <c r="C191">
+        <v>8.19227909204341e-05</v>
+      </c>
+      <c r="D191">
+        <v>0.999703817602057</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>4.06201920231798</v>
+      </c>
+      <c r="B192">
+        <v>14</v>
+      </c>
+      <c r="C192">
+        <v>8.82245440681598e-05</v>
+      </c>
+      <c r="D192">
+        <v>0.999792042146125</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>4.09267638593623</v>
+      </c>
+      <c r="B193">
+        <v>3</v>
+      </c>
+      <c r="C193">
+        <v>1.89052594431771e-05</v>
+      </c>
+      <c r="D193">
+        <v>0.999810947405568</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>4.12310562561766</v>
+      </c>
+      <c r="B194">
+        <v>6</v>
+      </c>
+      <c r="C194">
+        <v>3.78105188863542e-05</v>
+      </c>
+      <c r="D194">
+        <v>0.999848757924455</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>4.15331193145904</v>
+      </c>
+      <c r="B195">
+        <v>7</v>
+      </c>
+      <c r="C195">
+        <v>4.41122720340799e-05</v>
+      </c>
+      <c r="D195">
+        <v>0.999892870196489</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>4.18330013267038</v>
+      </c>
+      <c r="B196">
+        <v>2</v>
+      </c>
+      <c r="C196">
+        <v>1.26035062954514e-05</v>
+      </c>
+      <c r="D196">
+        <v>0.999905473702784</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>4.24264068711928</v>
+      </c>
+      <c r="B197">
+        <v>2</v>
+      </c>
+      <c r="C197">
+        <v>1.26035062954514e-05</v>
+      </c>
+      <c r="D197">
+        <v>0.99991807720908</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>4.27200187265877</v>
+      </c>
+      <c r="B198">
+        <v>2</v>
+      </c>
+      <c r="C198">
+        <v>1.26035062954514e-05</v>
+      </c>
+      <c r="D198">
+        <v>0.999930680715375</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>4.30116263352131</v>
+      </c>
+      <c r="B199">
+        <v>4</v>
+      </c>
+      <c r="C199">
+        <v>2.52070125909028e-05</v>
+      </c>
+      <c r="D199">
+        <v>0.999955887727966</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>4.33012701892219</v>
+      </c>
+      <c r="B200">
+        <v>2</v>
+      </c>
+      <c r="C200">
+        <v>1.26035062954514e-05</v>
+      </c>
+      <c r="D200">
+        <v>0.999968491234261</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>4.38748219369606</v>
+      </c>
+      <c r="B201">
+        <v>2</v>
+      </c>
+      <c r="C201">
+        <v>1.26035062954514e-05</v>
+      </c>
+      <c r="D201">
+        <v>0.999981094740557</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>4.47213595499958</v>
+      </c>
+      <c r="B202">
+        <v>2</v>
+      </c>
+      <c r="C202">
+        <v>1.26035062954514e-05</v>
+      </c>
+      <c r="D202">
+        <v>0.999993698246852</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>4.5</v>
+      </c>
+      <c r="B203">
+        <v>1</v>
+      </c>
+      <c r="C203">
+        <v>6.3017531477257e-06</v>
+      </c>
+      <c r="D203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204"/>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两点相关函数 / Two-Point Correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_fft_radial_shells_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porosity</t>
+        </is>
+      </c>
+      <c r="B209">
+        <v>0.394660949707031</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B210">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial bins</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bin_0_origin_only; bin_k: (k-1)*h &lt; distance &lt;= k*h</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalization</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joint_probability; C(0)=porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius upper edge (um)</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displacement count</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean distance (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>0</v>
+      </c>
+      <c r="B215">
+        <v>0.394660949707031</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
+      <c r="D215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>0.5</v>
+      </c>
+      <c r="B216">
+        <v>0.272056579589844</v>
+      </c>
+      <c r="C216">
+        <v>6</v>
+      </c>
+      <c r="D216">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>1</v>
+      </c>
+      <c r="B217">
+        <v>0.226334498478816</v>
+      </c>
+      <c r="C217">
+        <v>26</v>
+      </c>
+      <c r="D217">
+        <v>0.82359556171208</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>1.5</v>
+      </c>
+      <c r="B218">
+        <v>0.188593885633681</v>
+      </c>
+      <c r="C218">
+        <v>90</v>
+      </c>
+      <c r="D218">
+        <v>1.31330283768748</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>2</v>
+      </c>
+      <c r="B219">
+        <v>0.175237741043319</v>
+      </c>
+      <c r="C219">
+        <v>134</v>
+      </c>
+      <c r="D219">
+        <v>1.76619125712671</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>2.5</v>
+      </c>
+      <c r="B220">
+        <v>0.171637483345446</v>
+      </c>
+      <c r="C220">
+        <v>258</v>
+      </c>
+      <c r="D220">
+        <v>2.25329087515144</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>3</v>
+      </c>
+      <c r="B221">
+        <v>0.169719621611804</v>
+      </c>
+      <c r="C221">
+        <v>410</v>
+      </c>
+      <c r="D221">
+        <v>2.77015092047628</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>3.5</v>
+      </c>
+      <c r="B222">
+        <v>0.168391779849404</v>
+      </c>
+      <c r="C222">
+        <v>494</v>
+      </c>
+      <c r="D222">
+        <v>3.26511495914839</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>4</v>
+      </c>
+      <c r="B223">
+        <v>0.167141679404438</v>
+      </c>
+      <c r="C223">
+        <v>690</v>
+      </c>
+      <c r="D223">
+        <v>3.74137726298534</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>4.5</v>
+      </c>
+      <c r="B224">
+        <v>0.165865408407675</v>
+      </c>
+      <c r="C224">
+        <v>962</v>
+      </c>
+      <c r="D224">
+        <v>4.25479734207796</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>5</v>
+      </c>
+      <c r="B225">
+        <v>0.164734915088869</v>
+      </c>
+      <c r="C225">
+        <v>1098</v>
+      </c>
+      <c r="D225">
+        <v>4.75998893674797</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>5.5</v>
+      </c>
+      <c r="B226">
+        <v>0.163967344194523</v>
+      </c>
+      <c r="C226">
+        <v>1406</v>
+      </c>
+      <c r="D226">
+        <v>5.25297061080461</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>6</v>
+      </c>
+      <c r="B227">
+        <v>0.163293231727204</v>
+      </c>
+      <c r="C227">
+        <v>1578</v>
+      </c>
+      <c r="D227">
+        <v>5.7433060626392</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>6.5</v>
+      </c>
+      <c r="B228">
+        <v>0.162619542555719</v>
+      </c>
+      <c r="C228">
+        <v>2018</v>
+      </c>
+      <c r="D228">
+        <v>6.24308779578354</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>7</v>
+      </c>
+      <c r="B229">
+        <v>0.161890064112454</v>
+      </c>
+      <c r="C229">
+        <v>2342</v>
+      </c>
+      <c r="D229">
+        <v>6.75452277955052</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>7.5</v>
+      </c>
+      <c r="B230">
+        <v>0.161214424428744</v>
+      </c>
+      <c r="C230">
+        <v>2634</v>
+      </c>
+      <c r="D230">
+        <v>7.25880828593797</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>8</v>
+      </c>
+      <c r="B231">
+        <v>0.160540357466037</v>
+      </c>
+      <c r="C231">
+        <v>2930</v>
+      </c>
+      <c r="D231">
+        <v>7.7481595567505</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>8.5</v>
+      </c>
+      <c r="B232">
+        <v>0.15983210613558</v>
+      </c>
+      <c r="C232">
+        <v>3402</v>
+      </c>
+      <c r="D232">
+        <v>8.24275983872338</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>9</v>
+      </c>
+      <c r="B233">
+        <v>0.159192861128509</v>
+      </c>
+      <c r="C233">
+        <v>3926</v>
+      </c>
+      <c r="D233">
+        <v>8.74722614715433</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>9.5</v>
+      </c>
+      <c r="B234">
+        <v>0.158631338628312</v>
+      </c>
+      <c r="C234">
+        <v>4266</v>
+      </c>
+      <c r="D234">
+        <v>9.24875254641385</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>10</v>
+      </c>
+      <c r="B235">
+        <v>0.158176799556418</v>
+      </c>
+      <c r="C235">
+        <v>4730</v>
+      </c>
+      <c r="D235">
+        <v>9.74564847205822</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>10.5</v>
+      </c>
+      <c r="B236">
+        <v>0.157716476246579</v>
+      </c>
+      <c r="C236">
+        <v>5510</v>
+      </c>
+      <c r="D236">
+        <v>10.2542063522575</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>11</v>
+      </c>
+      <c r="B237">
+        <v>0.157334164122548</v>
+      </c>
+      <c r="C237">
+        <v>5562</v>
+      </c>
+      <c r="D237">
+        <v>10.7542478228895</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>11.5</v>
+      </c>
+      <c r="B238">
+        <v>0.156996251194042</v>
+      </c>
+      <c r="C238">
+        <v>6410</v>
+      </c>
+      <c r="D238">
+        <v>11.244987895373</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>12</v>
+      </c>
+      <c r="B239">
+        <v>0.156722836540096</v>
+      </c>
+      <c r="C239">
+        <v>6894</v>
+      </c>
+      <c r="D239">
+        <v>11.7450714339387</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>12.5</v>
+      </c>
+      <c r="B240">
+        <v>0.156456659823775</v>
+      </c>
+      <c r="C240">
+        <v>7490</v>
+      </c>
+      <c r="D240">
+        <v>12.2441426243554</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>13</v>
+      </c>
+      <c r="B241">
+        <v>0.156185033737704</v>
+      </c>
+      <c r="C241">
+        <v>8258</v>
+      </c>
+      <c r="D241">
+        <v>12.7444225452559</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>13.5</v>
+      </c>
+      <c r="B242">
+        <v>0.155888219608157</v>
+      </c>
+      <c r="C242">
+        <v>8994</v>
+      </c>
+      <c r="D242">
+        <v>13.2528519154988</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>14</v>
+      </c>
+      <c r="B243">
+        <v>0.155610670307393</v>
+      </c>
+      <c r="C243">
+        <v>9446</v>
+      </c>
+      <c r="D243">
+        <v>13.7542803671108</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>14.5</v>
+      </c>
+      <c r="B244">
+        <v>0.155407928326107</v>
+      </c>
+      <c r="C244">
+        <v>9978</v>
+      </c>
+      <c r="D244">
+        <v>14.2483018118451</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>15</v>
+      </c>
+      <c r="B245">
+        <v>0.155216742426687</v>
+      </c>
+      <c r="C245">
+        <v>11138</v>
+      </c>
+      <c r="D245">
+        <v>14.7478143756516</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>15.5</v>
+      </c>
+      <c r="B246">
+        <v>0.155072678604942</v>
+      </c>
+      <c r="C246">
+        <v>11406</v>
+      </c>
+      <c r="D246">
+        <v>15.2452282287867</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>16</v>
+      </c>
+      <c r="B247">
+        <v>0.154921714828218</v>
+      </c>
+      <c r="C247">
+        <v>12575</v>
+      </c>
+      <c r="D247">
+        <v>15.7433814113418</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>16.5</v>
+      </c>
+      <c r="B248">
+        <v>0.154787946014594</v>
+      </c>
+      <c r="C248">
+        <v>12848</v>
+      </c>
+      <c r="D248">
+        <v>16.2480191911098</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>17</v>
+      </c>
+      <c r="B249">
+        <v>0.154674369343873</v>
+      </c>
+      <c r="C249">
+        <v>12060</v>
+      </c>
+      <c r="D249">
+        <v>16.7498118527173</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>17.5</v>
+      </c>
+      <c r="B250">
+        <v>0.154586575468368</v>
+      </c>
+      <c r="C250">
+        <v>11804</v>
+      </c>
+      <c r="D250">
+        <v>17.2477889982035</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>18</v>
+      </c>
+      <c r="B251">
+        <v>0.154531021783035</v>
+      </c>
+      <c r="C251">
+        <v>11016</v>
+      </c>
+      <c r="D251">
+        <v>17.7466461218484</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>18.5</v>
+      </c>
+      <c r="B252">
+        <v>0.154414596557617</v>
+      </c>
+      <c r="C252">
+        <v>10700</v>
+      </c>
+      <c r="D252">
+        <v>18.2476461964778</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>19</v>
+      </c>
+      <c r="B253">
+        <v>0.154308427792682</v>
+      </c>
+      <c r="C253">
+        <v>9756</v>
+      </c>
+      <c r="D253">
+        <v>18.7461608461768</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>19.5</v>
+      </c>
+      <c r="B254">
+        <v>0.154218352781827</v>
+      </c>
+      <c r="C254">
+        <v>9224</v>
+      </c>
+      <c r="D254">
+        <v>19.2443623593903</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>20</v>
+      </c>
+      <c r="B255">
+        <v>0.154097827472197</v>
+      </c>
+      <c r="C255">
+        <v>8408</v>
+      </c>
+      <c r="D255">
+        <v>19.7427539394596</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>20.5</v>
+      </c>
+      <c r="B256">
+        <v>0.154006913984199</v>
+      </c>
+      <c r="C256">
+        <v>7452</v>
+      </c>
+      <c r="D256">
+        <v>20.2349524648069</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>21</v>
+      </c>
+      <c r="B257">
+        <v>0.15391245321794</v>
+      </c>
+      <c r="C257">
+        <v>7040</v>
+      </c>
+      <c r="D257">
+        <v>20.7366941177926</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>21.5</v>
+      </c>
+      <c r="B258">
+        <v>0.153785446009685</v>
+      </c>
+      <c r="C258">
+        <v>5820</v>
+      </c>
+      <c r="D258">
+        <v>21.2419860619221</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>22</v>
+      </c>
+      <c r="B259">
+        <v>0.153613900356605</v>
+      </c>
+      <c r="C259">
+        <v>4880</v>
+      </c>
+      <c r="D259">
+        <v>21.7372039907627</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>22.5</v>
+      </c>
+      <c r="B260">
+        <v>0.153447670665214</v>
+      </c>
+      <c r="C260">
+        <v>3936</v>
+      </c>
+      <c r="D260">
+        <v>22.2302479362391</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>23</v>
+      </c>
+      <c r="B261">
+        <v>0.153252642645205</v>
+      </c>
+      <c r="C261">
+        <v>2999</v>
+      </c>
+      <c r="D261">
+        <v>22.7334385317465</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>23.5</v>
+      </c>
+      <c r="B262">
+        <v>0.153017541027944</v>
+      </c>
+      <c r="C262">
+        <v>2180</v>
+      </c>
+      <c r="D262">
+        <v>23.2369587045059</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>24</v>
+      </c>
+      <c r="B263">
+        <v>0.15267421581127</v>
+      </c>
+      <c r="C263">
+        <v>1620</v>
+      </c>
+      <c r="D263">
+        <v>23.7279225769148</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>24.5</v>
+      </c>
+      <c r="B264">
+        <v>0.152333303792587</v>
+      </c>
+      <c r="C264">
+        <v>1208</v>
+      </c>
+      <c r="D264">
+        <v>24.2151258882127</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>25</v>
+      </c>
+      <c r="B265">
+        <v>0.152057105062367</v>
+      </c>
+      <c r="C265">
+        <v>942</v>
+      </c>
+      <c r="D265">
+        <v>24.7383759194601</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>25.5</v>
+      </c>
+      <c r="B266">
+        <v>0.151641701998776</v>
+      </c>
+      <c r="C266">
+        <v>584</v>
+      </c>
+      <c r="D266">
+        <v>25.2823739766508</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>26</v>
+      </c>
+      <c r="B267">
+        <v>0.151251940660074</v>
+      </c>
+      <c r="C267">
+        <v>284</v>
+      </c>
+      <c r="D267">
+        <v>25.7666230311241</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>26.5</v>
+      </c>
+      <c r="B268">
+        <v>0.151068528493245</v>
+      </c>
+      <c r="C268">
+        <v>192</v>
+      </c>
+      <c r="D268">
+        <v>26.1687296580041</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>27</v>
+      </c>
+      <c r="B269">
+        <v>0.151038756737342</v>
+      </c>
+      <c r="C269">
+        <v>104</v>
+      </c>
+      <c r="D269">
+        <v>26.6774814912972</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>27.5</v>
+      </c>
+      <c r="B270">
+        <v>0.151204744974772</v>
+      </c>
+      <c r="C270">
+        <v>24</v>
+      </c>
+      <c r="D270">
+        <v>27.2129968013123</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>28</v>
+      </c>
+      <c r="B271">
+        <v>0.15087890625</v>
+      </c>
+      <c r="C271">
+        <v>1</v>
+      </c>
+      <c r="D271">
+        <v>27.712812921102</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x displacement (um)</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>0</v>
+      </c>
+      <c r="B273">
+        <v>0.394660949707031</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>0.5</v>
+      </c>
+      <c r="B274">
+        <v>0.267848968505859</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>1</v>
+      </c>
+      <c r="B275">
+        <v>0.205821990966797</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>1.5</v>
+      </c>
+      <c r="B276">
+        <v>0.178218841552734</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>2</v>
+      </c>
+      <c r="B277">
+        <v>0.174488067626953</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>2.5</v>
+      </c>
+      <c r="B278">
+        <v>0.171653747558594</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>3</v>
+      </c>
+      <c r="B279">
+        <v>0.169742584228516</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>3.5</v>
+      </c>
+      <c r="B280">
+        <v>0.168052673339844</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>4</v>
+      </c>
+      <c r="B281">
+        <v>0.166145324707031</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>4.5</v>
+      </c>
+      <c r="B282">
+        <v>0.164905548095703</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>5</v>
+      </c>
+      <c r="B283">
+        <v>0.163806915283203</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>5.5</v>
+      </c>
+      <c r="B284">
+        <v>0.162590026855469</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>6</v>
+      </c>
+      <c r="B285">
+        <v>0.161640167236328</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>6.5</v>
+      </c>
+      <c r="B286">
+        <v>0.160934448242188</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>7</v>
+      </c>
+      <c r="B287">
+        <v>0.161384582519531</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>7.5</v>
+      </c>
+      <c r="B288">
+        <v>0.161605834960938</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>8</v>
+      </c>
+      <c r="B289">
+        <v>0.161037445068359</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>8.5</v>
+      </c>
+      <c r="B290">
+        <v>0.159870147705078</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>9</v>
+      </c>
+      <c r="B291">
+        <v>0.159294128417969</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>9.5</v>
+      </c>
+      <c r="B292">
+        <v>0.158958435058594</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>10</v>
+      </c>
+      <c r="B293">
+        <v>0.158195495605469</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>10.5</v>
+      </c>
+      <c r="B294">
+        <v>0.156970977783203</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>11</v>
+      </c>
+      <c r="B295">
+        <v>0.15533447265625</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>11.5</v>
+      </c>
+      <c r="B296">
+        <v>0.155044555664062</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>12</v>
+      </c>
+      <c r="B297">
+        <v>0.155879974365234</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>12.5</v>
+      </c>
+      <c r="B298">
+        <v>0.155906677246094</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>13</v>
+      </c>
+      <c r="B299">
+        <v>0.154960632324219</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>13.5</v>
+      </c>
+      <c r="B300">
+        <v>0.154060363769531</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>14</v>
+      </c>
+      <c r="B301">
+        <v>0.153873443603516</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>14.5</v>
+      </c>
+      <c r="B302">
+        <v>0.153682708740234</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>15</v>
+      </c>
+      <c r="B303">
+        <v>0.153610229492188</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>15.5</v>
+      </c>
+      <c r="B304">
+        <v>0.152572631835938</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>16</v>
+      </c>
+      <c r="B305">
+        <v>0.151840209960938</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y displacement (um)</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>0</v>
+      </c>
+      <c r="B307">
+        <v>0.394660949707031</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>0.5</v>
+      </c>
+      <c r="B308">
+        <v>0.267757415771484</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>1</v>
+      </c>
+      <c r="B309">
+        <v>0.205524444580078</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>1.5</v>
+      </c>
+      <c r="B310">
+        <v>0.177753448486328</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>2</v>
+      </c>
+      <c r="B311">
+        <v>0.172237396240234</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>2.5</v>
+      </c>
+      <c r="B312">
+        <v>0.169456481933594</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>3</v>
+      </c>
+      <c r="B313">
+        <v>0.168865203857422</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>3.5</v>
+      </c>
+      <c r="B314">
+        <v>0.168186187744141</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>4</v>
+      </c>
+      <c r="B315">
+        <v>0.167133331298828</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>4.5</v>
+      </c>
+      <c r="B316">
+        <v>0.165332794189453</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>5</v>
+      </c>
+      <c r="B317">
+        <v>0.163719177246094</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>5.5</v>
+      </c>
+      <c r="B318">
+        <v>0.1634521484375</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>6</v>
+      </c>
+      <c r="B319">
+        <v>0.162685394287109</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>6.5</v>
+      </c>
+      <c r="B320">
+        <v>0.161148071289062</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>7</v>
+      </c>
+      <c r="B321">
+        <v>0.160041809082031</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>7.5</v>
+      </c>
+      <c r="B322">
+        <v>0.159854888916016</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>8</v>
+      </c>
+      <c r="B323">
+        <v>0.159332275390625</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>8.5</v>
+      </c>
+      <c r="B324">
+        <v>0.15875244140625</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>9</v>
+      </c>
+      <c r="B325">
+        <v>0.157840728759766</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>9.5</v>
+      </c>
+      <c r="B326">
+        <v>0.157726287841797</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>10</v>
+      </c>
+      <c r="B327">
+        <v>0.157791137695312</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>10.5</v>
+      </c>
+      <c r="B328">
+        <v>0.157272338867188</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>11</v>
+      </c>
+      <c r="B329">
+        <v>0.157962799072266</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>11.5</v>
+      </c>
+      <c r="B330">
+        <v>0.157699584960938</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>12</v>
+      </c>
+      <c r="B331">
+        <v>0.157207489013672</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>12.5</v>
+      </c>
+      <c r="B332">
+        <v>0.155570983886719</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>13</v>
+      </c>
+      <c r="B333">
+        <v>0.154155731201172</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>13.5</v>
+      </c>
+      <c r="B334">
+        <v>0.153877258300781</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>14</v>
+      </c>
+      <c r="B335">
+        <v>0.153488159179688</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>14.5</v>
+      </c>
+      <c r="B336">
+        <v>0.153057098388672</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>15</v>
+      </c>
+      <c r="B337">
+        <v>0.15240478515625</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>15.5</v>
+      </c>
+      <c r="B338">
+        <v>0.152587890625</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>16</v>
+      </c>
+      <c r="B339">
+        <v>0.152473449707031</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z displacement (um)</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>0</v>
+      </c>
+      <c r="B341">
+        <v>0.394660949707031</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>0.5</v>
+      </c>
+      <c r="B342">
+        <v>0.280563354492188</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>1</v>
+      </c>
+      <c r="B343">
+        <v>0.217681884765625</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>1.5</v>
+      </c>
+      <c r="B344">
+        <v>0.187076568603516</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>2</v>
+      </c>
+      <c r="B345">
+        <v>0.1763916015625</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>2.5</v>
+      </c>
+      <c r="B346">
+        <v>0.170963287353516</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>3</v>
+      </c>
+      <c r="B347">
+        <v>0.168464660644531</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <v>3.5</v>
+      </c>
+      <c r="B348">
+        <v>0.167400360107422</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>4</v>
+      </c>
+      <c r="B349">
+        <v>0.166229248046875</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>4.5</v>
+      </c>
+      <c r="B350">
+        <v>0.166126251220703</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>5</v>
+      </c>
+      <c r="B351">
+        <v>0.165515899658203</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>5.5</v>
+      </c>
+      <c r="B352">
+        <v>0.164058685302734</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>6</v>
+      </c>
+      <c r="B353">
+        <v>0.162811279296875</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <v>6.5</v>
+      </c>
+      <c r="B354">
+        <v>0.162368774414062</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <v>7</v>
+      </c>
+      <c r="B355">
+        <v>0.1614990234375</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <v>7.5</v>
+      </c>
+      <c r="B356">
+        <v>0.161342620849609</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <v>8</v>
+      </c>
+      <c r="B357">
+        <v>0.160675048828125</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358">
+        <v>8.5</v>
+      </c>
+      <c r="B358">
+        <v>0.159080505371094</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <v>9</v>
+      </c>
+      <c r="B359">
+        <v>0.158821105957031</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <v>9.5</v>
+      </c>
+      <c r="B360">
+        <v>0.158554077148438</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361">
+        <v>10</v>
+      </c>
+      <c r="B361">
+        <v>0.158744812011719</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <v>10.5</v>
+      </c>
+      <c r="B362">
+        <v>0.158763885498047</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <v>11</v>
+      </c>
+      <c r="B363">
+        <v>0.158897399902344</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <v>11.5</v>
+      </c>
+      <c r="B364">
+        <v>0.158233642578125</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365">
+        <v>12</v>
+      </c>
+      <c r="B365">
+        <v>0.157501220703125</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366">
+        <v>12.5</v>
+      </c>
+      <c r="B366">
+        <v>0.156784057617188</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367">
+        <v>13</v>
+      </c>
+      <c r="B367">
+        <v>0.155906677246094</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368">
+        <v>13.5</v>
+      </c>
+      <c r="B368">
+        <v>0.156669616699219</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369">
+        <v>14</v>
+      </c>
+      <c r="B369">
+        <v>0.157238006591797</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370">
+        <v>14.5</v>
+      </c>
+      <c r="B370">
+        <v>0.157859802246094</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371">
+        <v>15</v>
+      </c>
+      <c r="B371">
+        <v>0.158180236816406</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372">
+        <v>15.5</v>
+      </c>
+      <c r="B372">
+        <v>0.157844543457031</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373">
+        <v>16</v>
+      </c>
+      <c r="B373">
+        <v>0.158256530761719</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>